--- a/products.xlsx
+++ b/products.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\linear algebra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{259BA521-3D2A-4F87-BCF4-691D8B6586FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53EA523-950F-4F5C-B505-C6AB7AAAC854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Siuuuuuuuuuuu" sheetId="1" r:id="rId1"/>
+    <sheet name="Siuuuuu 2" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="121">
   <si>
     <t>نام كالا</t>
   </si>
@@ -43,298 +43,346 @@
     <t>مشخصات فني 2</t>
   </si>
   <si>
-    <t>BIO- بايورومينا دامي 100گرمي</t>
+    <t>اسپري زاور اسب 50 ميل</t>
+  </si>
+  <si>
+    <t>عدد</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1403/05</t>
+  </si>
+  <si>
+    <t>1.200.000</t>
+  </si>
+  <si>
+    <t>اسپري زاور پت 50 ميل</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1403/05</t>
+  </si>
+  <si>
+    <t>1.000.000</t>
+  </si>
+  <si>
+    <t>اسپري زاور دامي 50 ميل</t>
+  </si>
+  <si>
+    <t>عدد</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1403/05</t>
+  </si>
+  <si>
+    <t>1.000.000</t>
+  </si>
+  <si>
+    <t>پارسي لاکت +FB نامحلول 10کيلويي</t>
+  </si>
+  <si>
+    <t>کيلوگرم</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1.780.000</t>
+  </si>
+  <si>
+    <t>پارسي لاکت fb+ طيوري 1کيلوگرمي</t>
+  </si>
+  <si>
+    <t>کيلوگرم</t>
+  </si>
+  <si>
+    <t>1405/04</t>
+  </si>
+  <si>
+    <t>031024231203</t>
+  </si>
+  <si>
+    <t>4.500.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پارسي لاکت fb+دامي1 کيلوگرمي </t>
+  </si>
+  <si>
+    <t>کيلوگرم</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1.800.000</t>
+  </si>
+  <si>
+    <t>پارسي لاکت آبزيان 1کيلوگرمي</t>
+  </si>
+  <si>
+    <t>کيلوگرم</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2.300.000</t>
+  </si>
+  <si>
+    <t>پارسي لاکت آبزيان 500 گرمي</t>
+  </si>
+  <si>
+    <t>کيسه</t>
+  </si>
+  <si>
+    <t>1406/06</t>
+  </si>
+  <si>
+    <t>041204021205</t>
+  </si>
+  <si>
+    <t>2.420.000</t>
+  </si>
+  <si>
+    <t>پارسي لاکت اسب 120 گرمي</t>
   </si>
   <si>
     <t>قوطي</t>
   </si>
   <si>
-    <t>1.800.000</t>
-  </si>
-  <si>
-    <t>BIO-پرندگان زينتي 80 گرميpoul-ws</t>
+    <t>040321121228</t>
+  </si>
+  <si>
+    <t>2.205.000</t>
+  </si>
+  <si>
+    <t>پارسي لاکت اسب 1کيلوگرمي</t>
   </si>
   <si>
     <t>قوطي</t>
   </si>
   <si>
-    <t>0700180</t>
-  </si>
-  <si>
-    <t>2.700.000</t>
-  </si>
-  <si>
-    <t>BIO-پروبيوتيک آبزيان 500 گرمي</t>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2.180.000</t>
+  </si>
+  <si>
+    <t>پارسي لاکت اسب 500 گرمي</t>
   </si>
   <si>
     <t>کيسه</t>
   </si>
   <si>
-    <t>0100035</t>
-  </si>
-  <si>
-    <t>3.400.000</t>
-  </si>
-  <si>
-    <t>BIO-پروبيوتيک اسب 500 گرمي</t>
+    <t>040321121208</t>
+  </si>
+  <si>
+    <t>2.900.000</t>
+  </si>
+  <si>
+    <t>پارسي لاکت انساني</t>
+  </si>
+  <si>
+    <t>بسته</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>پارسي لاکت پرسي زايم 1 کيلويي</t>
+  </si>
+  <si>
+    <t>کيلوگرم</t>
+  </si>
+  <si>
+    <t>1406/04</t>
+  </si>
+  <si>
+    <t>050402021253</t>
+  </si>
+  <si>
+    <t>7.262.000</t>
+  </si>
+  <si>
+    <t>پارسي لاکت پرندگان زينتي 120 گرمي</t>
   </si>
   <si>
     <t>قوطي</t>
   </si>
   <si>
-    <t>2028/04</t>
-  </si>
-  <si>
-    <t>0300055</t>
-  </si>
-  <si>
-    <t>6.200.000</t>
-  </si>
-  <si>
-    <t>BIO-پروبيوتيک اشتها آور دام</t>
-  </si>
-  <si>
-    <t>بسته</t>
-  </si>
-  <si>
-    <t>2028/06</t>
-  </si>
-  <si>
-    <t>16015</t>
-  </si>
-  <si>
-    <t>17.000.000</t>
-  </si>
-  <si>
-    <t>BIO-پروبيوتيک پرندگان زينتي 5 گرمي</t>
+    <t>041003051213</t>
+  </si>
+  <si>
+    <t>2.587.000</t>
+  </si>
+  <si>
+    <t>پارسي لاکت پرندگان زينتي 2 گرمي</t>
   </si>
   <si>
     <t>جعبه</t>
   </si>
   <si>
-    <t>0700169</t>
-  </si>
-  <si>
-    <t>2.900.000</t>
-  </si>
-  <si>
-    <t>BIO-پروبيوتيک خوراک آبزيان</t>
+    <t>041130231215</t>
+  </si>
+  <si>
+    <t>2.300.000</t>
+  </si>
+  <si>
+    <t>پارسي لاکت دامي 120 گرمي</t>
+  </si>
+  <si>
+    <t>قوطي</t>
+  </si>
+  <si>
+    <t>1407/02</t>
+  </si>
+  <si>
+    <t>050210091211</t>
+  </si>
+  <si>
+    <t>1.794.000</t>
+  </si>
+  <si>
+    <t>پارسي لاکت دامي 500 گرمي</t>
   </si>
   <si>
     <t>کيسه</t>
   </si>
   <si>
-    <t>1.120.000</t>
-  </si>
-  <si>
-    <t>BIO-پروبيوتيک زنبور عسل</t>
+    <t>1406/08</t>
+  </si>
+  <si>
+    <t>050223271201</t>
+  </si>
+  <si>
+    <t>3.459.000</t>
+  </si>
+  <si>
+    <t>پارسي لاکت سگ و گربه 120 گرمي</t>
   </si>
   <si>
     <t>قوطي</t>
   </si>
   <si>
-    <t>2027/06</t>
-  </si>
-  <si>
-    <t>110046</t>
-  </si>
-  <si>
-    <t>600.000</t>
-  </si>
-  <si>
-    <t>BIO-حيوانات خانگي 5 گرمي-pet</t>
+    <t>1406/08</t>
+  </si>
+  <si>
+    <t>050207031214</t>
+  </si>
+  <si>
+    <t>3.093.000</t>
+  </si>
+  <si>
+    <t>پارسي لاکت سگ و گربه 2 گرمي</t>
   </si>
   <si>
     <t>جعبه</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>2.900.000</t>
-  </si>
-  <si>
-    <t>bio-دامي رومينا 500گرمي</t>
-  </si>
-  <si>
-    <t>بسته</t>
-  </si>
-  <si>
-    <t>2028/06</t>
-  </si>
-  <si>
-    <t>0600224</t>
-  </si>
-  <si>
-    <t>4.900.000</t>
-  </si>
-  <si>
-    <t>Bio-سين بيوتيک محلول در آب طيور</t>
-  </si>
-  <si>
-    <t>بسته</t>
-  </si>
-  <si>
-    <t>2028/04</t>
-  </si>
-  <si>
-    <t>180005</t>
-  </si>
-  <si>
-    <t>4.350.000</t>
-  </si>
-  <si>
-    <t>BIO-ضد استرس طيور 100 گرمي</t>
-  </si>
-  <si>
-    <t>جعبه</t>
-  </si>
-  <si>
-    <t>2025/10</t>
-  </si>
-  <si>
-    <t>0500091</t>
-  </si>
-  <si>
-    <t>5.150.000</t>
-  </si>
-  <si>
-    <t>BIO-ضداسترس طيور120 گرمي</t>
-  </si>
-  <si>
-    <t>بطري</t>
+    <t>1406/08</t>
+  </si>
+  <si>
+    <t>050229331216</t>
+  </si>
+  <si>
+    <t>2.681.000</t>
+  </si>
+  <si>
+    <t>پارسي لاکت طيوري 120 گرمي</t>
+  </si>
+  <si>
+    <t>قوطي</t>
+  </si>
+  <si>
+    <t>1404/09</t>
+  </si>
+  <si>
+    <t>030303021233</t>
+  </si>
+  <si>
+    <t>935.000</t>
+  </si>
+  <si>
+    <t>پارسي لاکت طيوري 500 گرمي</t>
+  </si>
+  <si>
+    <t>کيسه</t>
+  </si>
+  <si>
+    <t>041007081203</t>
+  </si>
+  <si>
+    <t>2.550.000</t>
+  </si>
+  <si>
+    <t>سابوفلورا دامي 1 کيلوگرمي</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>350.000</t>
-  </si>
-  <si>
-    <t>BIO-طيور محلول در آب-500گ</t>
-  </si>
-  <si>
-    <t>ساشه</t>
-  </si>
-  <si>
-    <t>0500140</t>
-  </si>
-  <si>
-    <t>2.400.000</t>
-  </si>
-  <si>
-    <t>BIO-طيور مخلوط در دان-500گ</t>
-  </si>
-  <si>
-    <t>ساشه</t>
-  </si>
-  <si>
-    <t>2028/06</t>
-  </si>
-  <si>
-    <t>0400150</t>
-  </si>
-  <si>
-    <t>3.300.000</t>
-  </si>
-  <si>
-    <t>bio-مخمر دامي 1 کيلويي-رومي ست</t>
-  </si>
-  <si>
-    <t>کيلوگرم</t>
-  </si>
-  <si>
-    <t>1200121</t>
-  </si>
-  <si>
-    <t>2.900.000</t>
-  </si>
-  <si>
-    <t>bio-مخمر دامي 10 کيلويي رومي ست</t>
-  </si>
-  <si>
-    <t>کيسه</t>
-  </si>
-  <si>
-    <t>2027/12</t>
-  </si>
-  <si>
-    <t>1200113</t>
-  </si>
-  <si>
-    <t>29.800.000</t>
-  </si>
-  <si>
-    <t>BIO-مکمل اشتها آور دام</t>
-  </si>
-  <si>
-    <t>بسته</t>
-  </si>
-  <si>
-    <t>2028/05</t>
-  </si>
-  <si>
-    <t>15008</t>
-  </si>
-  <si>
-    <t>15.000.000</t>
-  </si>
-  <si>
-    <t>DiaCare-BIO ضداسهال دامي 10تايي</t>
-  </si>
-  <si>
-    <t>بسته</t>
-  </si>
-  <si>
-    <t>2027/06</t>
-  </si>
-  <si>
-    <t>140043</t>
-  </si>
-  <si>
-    <t>12.500.000</t>
-  </si>
-  <si>
-    <t>اسپري ضد عفوني کروپت</t>
+    <t>1403/08</t>
+  </si>
+  <si>
+    <t>0208071209</t>
+  </si>
+  <si>
+    <t>3.800.000</t>
+  </si>
+  <si>
+    <t>کورکومين محلول خوراکي 200 ml</t>
   </si>
   <si>
     <t>عدد</t>
   </si>
   <si>
-    <t xml:space="preserve">2024/07 </t>
-  </si>
-  <si>
-    <t>CP02</t>
-  </si>
-  <si>
-    <t>600.000</t>
+    <t>CP031002</t>
+  </si>
+  <si>
+    <t>2.890.000</t>
   </si>
   <si>
     <t>رديف</t>
   </si>
   <si>
+    <t xml:space="preserve"> 1406/06</t>
+  </si>
+  <si>
+    <t>1405/09</t>
+  </si>
+  <si>
+    <t>1406/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2026/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دسته بندی </t>
+  </si>
+  <si>
     <t>medicine</t>
-  </si>
-  <si>
-    <t>دسته بندی</t>
-  </si>
-  <si>
-    <t>2028/07</t>
-  </si>
-  <si>
-    <t>2027/10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/02 </t>
-  </si>
-  <si>
-    <t>2027/07</t>
-  </si>
-  <si>
-    <t>2028/02</t>
   </si>
 </sst>
 </file>
@@ -350,31 +398,31 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Bahnschrift Light SemiCondensed"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Bahnschrift Light SemiCondensed"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Bahnschrift Light SemiCondensed"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
-      <name val="Bahnschrift Light SemiCondensed"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Bahnschrift Light SemiCondensed"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -768,35 +816,35 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="3" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="3" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1079,14 +1127,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="28.1328125" customWidth="1"/>
     <col min="3" max="3" width="12.73046875" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="47.06640625" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="12.73046875" style="17" customWidth="1"/>
     <col min="7" max="7" width="21.1328125" customWidth="1"/>
     <col min="8" max="9" width="21.1328125" style="17" customWidth="1"/>
@@ -1094,7 +1142,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1118,7 +1166,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="21" customHeight="1">
@@ -1129,25 +1177,25 @@
         <v>7</v>
       </c>
       <c r="C2" s="4">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F2" s="18">
-        <v>1607142</v>
-      </c>
-      <c r="G2" s="3">
-        <v>600219</v>
+        <v>1071400</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="21" customHeight="1">
@@ -1155,28 +1203,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="8">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="F3" s="19">
-        <v>1800000</v>
+        <v>892860</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="21" customHeight="1">
@@ -1184,28 +1232,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" s="4">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="F4" s="18">
-        <v>3035714</v>
+        <v>892860</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="21" customHeight="1">
@@ -1213,28 +1261,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" s="8">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F5" s="19">
-        <v>5535714</v>
+        <v>1590000</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="21" customHeight="1">
@@ -1242,28 +1290,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="18">
+        <v>4017858</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="18">
-        <v>15178571</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>27</v>
-      </c>
       <c r="I6" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="21" customHeight="1">
@@ -1271,28 +1319,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" s="8">
-        <v>343</v>
+        <v>0</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="F7" s="19">
-        <v>1980000</v>
+        <v>1607000</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="21" customHeight="1">
@@ -1300,26 +1348,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4">
         <v>0</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F8" s="18">
-        <v>1000000</v>
-      </c>
-      <c r="G8" s="3"/>
+        <v>2054000</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="H8" s="14" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="21" customHeight="1">
@@ -1327,28 +1377,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C9" s="8">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F9" s="19">
-        <v>535714</v>
+        <v>2122000</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="21" customHeight="1">
@@ -1356,28 +1406,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C10" s="4">
-        <v>243</v>
+        <v>57</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="F10" s="18">
-        <v>1950000</v>
+        <v>1934610</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="21" customHeight="1">
@@ -1385,28 +1435,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C11" s="8">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F11" s="19">
-        <v>4375000</v>
+        <v>1946428</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="21" customHeight="1">
@@ -1414,28 +1464,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C12" s="4">
         <v>0</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="F12" s="18">
-        <v>3883928</v>
+        <v>2543000</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="21" customHeight="1">
@@ -1443,28 +1493,26 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C13" s="8">
+        <v>25</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="19">
         <v>0</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="19">
-        <v>4598214</v>
-      </c>
       <c r="G13" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="21" customHeight="1">
@@ -1472,28 +1520,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C14" s="4">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F14" s="18">
-        <v>312500</v>
+        <v>6370800</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="21" customHeight="1">
@@ -1501,28 +1549,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C15" s="8">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="D15" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>103</v>
-      </c>
       <c r="F15" s="19">
-        <v>2142857</v>
+        <v>2156250</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="21" customHeight="1">
@@ -1530,28 +1578,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C16" s="4">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="F16" s="18">
-        <v>2946428</v>
+        <v>1916670</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="21" customHeight="1">
@@ -1559,28 +1607,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C17" s="8">
-        <v>124</v>
+        <v>206</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="F17" s="19">
-        <v>2589285</v>
+        <v>1573680</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="21" customHeight="1">
@@ -1588,28 +1636,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C18" s="4">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F18" s="18">
-        <v>26607142</v>
+        <v>3034390</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="21" customHeight="1">
@@ -1617,28 +1665,28 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C19" s="8">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F19" s="19">
-        <v>13392857</v>
+        <v>2578130</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="21" customHeight="1">
@@ -1646,28 +1694,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C20" s="4">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F20" s="18">
-        <v>11160710</v>
+        <v>2234280</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="21" customHeight="1">
@@ -1675,42 +1723,129 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C21" s="8">
         <v>0</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F21" s="19">
-        <v>450000</v>
+        <v>835000</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I21" s="22" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="12">
-        <v>1836</v>
-      </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="23"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="21" customHeight="1">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" s="4">
+        <v>192</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F22" s="18">
+        <v>2233000</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="I22" s="22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="21" customHeight="1">
+      <c r="A23" s="6">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="19">
+        <v>3388000</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I23" s="22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="21" customHeight="1">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="4">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F24" s="18">
+        <v>2580357</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="I24" s="22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="17.25" customHeight="1">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="12">
+        <v>1391</v>
+      </c>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
